--- a/Tracker.xlsx
+++ b/Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\McJoseph\OneDrive\EMSI\AI\Agency\mini-pos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75D0ACA8-DC03-48D5-A159-CBE6AC5F6EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11513EF2-5908-4AF8-887D-5321A0C5A743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AEC04634-4814-46F6-9EC2-60EF29B767A5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="67">
   <si>
     <t>ID</t>
   </si>
@@ -231,9 +231,6 @@
   </si>
   <si>
     <t>DONE</t>
-  </si>
-  <si>
-    <t>PENDING</t>
   </si>
   <si>
     <t>Add manual shift start. Allow a shift to be started manually when needed. Add start button in all places applcable for users that are in a shift.</t>
@@ -331,7 +328,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B5E406E8-8395-4AD5-9AD5-9EFF0503E8A0}" name="Table1" displayName="Table1" ref="A1:H15" totalsRowShown="0">
   <autoFilter ref="A1:H15" xr:uid="{B5E406E8-8395-4AD5-9AD5-9EFF0503E8A0}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H15">
-    <sortCondition ref="G1:G15"/>
+    <sortCondition ref="H1:H15"/>
   </sortState>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{94516695-E9BB-46EF-83FC-FC9E35FA87B7}" name="ID"/>
@@ -704,70 +701,74 @@
     </row>
     <row r="2" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B2" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="3"/>
+      <c r="H2" s="3" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="3" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B3" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="3"/>
-    </row>
-    <row r="4" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="H3" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B4" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>15</v>
@@ -776,24 +777,24 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="B5" s="5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>15</v>
@@ -802,172 +803,170 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B7" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>15</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B8" s="5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>15</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B9" s="5">
+        <v>11</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>15</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="B10" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>64</v>
-      </c>
+      <c r="H10" s="3"/>
     </row>
     <row r="11" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="B11" s="5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>67</v>
-      </c>
+      <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="B12" s="5">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>11</v>
@@ -976,11 +975,9 @@
         <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>67</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="H12" s="3"/>
     </row>
     <row r="13" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
